--- a/InputData/cpi.xlsx
+++ b/InputData/cpi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{698147E0-8145-46CB-AA60-1ED82BEC5780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF52595-3A46-466C-A7C7-BDC2938CF93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-3780" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t>2nd half</t>
   </si>
   <si>
-    <t>Dec.</t>
-  </si>
-  <si>
     <t>–</t>
   </si>
   <si>
@@ -252,6 +249,10 @@
     <t>2020............................................................................. .</t>
   </si>
   <si>
+    <t>https://data.bls.gov/timeseries/CUUR0000SA0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>2021............................................................................. .</t>
   </si>
   <si>
@@ -261,24 +262,23 @@
     <t>2023............................................................................. .</t>
   </si>
   <si>
-    <t>https://data.bls.gov/pdq/SurveyOutputServlet</t>
+    <t>2024............................................................................. .</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="#0.0"/>
-    <numFmt numFmtId="167" formatCode="#0.000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="178" formatCode="#0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -286,7 +286,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -294,15 +294,61 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color indexed="8"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -326,30 +372,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -652,87 +712,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{80C720B1-7B35-4397-8216-EC99C9E8CF3A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="15" max="15" width="28.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="15" width="28.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -749,29 +814,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>34.799999999999997</v>
@@ -782,16 +844,17 @@
       <c r="F6">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>36.700000000000003</v>
@@ -799,19 +862,21 @@
       <c r="E7">
         <v>6.2</v>
       </c>
-      <c r="F7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F7" s="11">
+        <f>(D7-D6)/D6*100</f>
+        <v>5.4597701149425459</v>
+      </c>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>38.799999999999997</v>
@@ -819,19 +884,21 @@
       <c r="E8">
         <v>5.6</v>
       </c>
-      <c r="F8">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" s="11">
+        <f t="shared" ref="F8:F62" si="0">(D8-D7)/D7*100</f>
+        <v>5.7220708446866322</v>
+      </c>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>40.5</v>
@@ -839,19 +906,21 @@
       <c r="E9">
         <v>3.3</v>
       </c>
-      <c r="F9">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9" s="11">
+        <f t="shared" si="0"/>
+        <v>4.3814432989690797</v>
+      </c>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>41.8</v>
@@ -859,19 +928,21 @@
       <c r="E10">
         <v>3.4</v>
       </c>
-      <c r="F10">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10" s="11">
+        <f t="shared" si="0"/>
+        <v>3.2098765432098699</v>
+      </c>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>44.4</v>
@@ -879,19 +950,21 @@
       <c r="E11">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F11">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" s="11">
+        <f t="shared" si="0"/>
+        <v>6.2200956937799079</v>
+      </c>
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>49.3</v>
@@ -899,19 +972,21 @@
       <c r="E12">
         <v>12.3</v>
       </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F12" s="11">
+        <f t="shared" si="0"/>
+        <v>11.036036036036032</v>
+      </c>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13">
         <v>53.8</v>
@@ -919,19 +994,21 @@
       <c r="E13">
         <v>6.9</v>
       </c>
-      <c r="F13">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F13" s="11">
+        <f t="shared" si="0"/>
+        <v>9.1277890466531435</v>
+      </c>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14">
         <v>56.9</v>
@@ -939,19 +1016,21 @@
       <c r="E14">
         <v>4.9000000000000004</v>
       </c>
-      <c r="F14">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F14" s="11">
+        <f t="shared" si="0"/>
+        <v>5.7620817843866208</v>
+      </c>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15">
         <v>60.6</v>
@@ -959,19 +1038,21 @@
       <c r="E15">
         <v>6.7</v>
       </c>
-      <c r="F15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F15" s="11">
+        <f t="shared" si="0"/>
+        <v>6.5026362038664383</v>
+      </c>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16">
         <v>65.2</v>
@@ -979,19 +1060,21 @@
       <c r="E16">
         <v>9</v>
       </c>
-      <c r="F16">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F16" s="11">
+        <f t="shared" si="0"/>
+        <v>7.5907590759075925</v>
+      </c>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17">
         <v>72.599999999999994</v>
@@ -999,19 +1082,21 @@
       <c r="E17">
         <v>13.3</v>
       </c>
-      <c r="F17">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F17" s="11">
+        <f t="shared" si="0"/>
+        <v>11.349693251533727</v>
+      </c>
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18">
         <v>82.4</v>
@@ -1019,19 +1104,21 @@
       <c r="E18">
         <v>12.5</v>
       </c>
-      <c r="F18">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F18" s="11">
+        <f t="shared" si="0"/>
+        <v>13.498622589531697</v>
+      </c>
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19">
         <v>90.9</v>
@@ -1039,19 +1126,21 @@
       <c r="E19">
         <v>8.9</v>
       </c>
-      <c r="F19">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F19" s="11">
+        <f t="shared" si="0"/>
+        <v>10.315533980582524</v>
+      </c>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20">
         <v>96.5</v>
@@ -1059,19 +1148,21 @@
       <c r="E20">
         <v>3.8</v>
       </c>
-      <c r="F20">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F20" s="11">
+        <f t="shared" si="0"/>
+        <v>6.160616061606154</v>
+      </c>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21">
         <v>99.6</v>
@@ -1079,1029 +1170,1294 @@
       <c r="E21">
         <v>3.8</v>
       </c>
-      <c r="F21">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F21" s="11">
+        <f t="shared" si="0"/>
+        <v>3.2124352331606163</v>
+      </c>
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="7">
+        <v>35</v>
+      </c>
+      <c r="B22">
         <v>102.9</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22">
         <v>104.9</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22">
         <v>103.9</v>
       </c>
       <c r="E22">
         <v>3.9</v>
       </c>
-      <c r="F22">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F22" s="11">
+        <f t="shared" si="0"/>
+        <v>4.3172690763052319</v>
+      </c>
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="7">
+        <v>36</v>
+      </c>
+      <c r="B23">
         <v>106.6</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23">
         <v>108.5</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23">
         <v>107.6</v>
       </c>
       <c r="E23">
         <v>3.8</v>
       </c>
-      <c r="F23">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F23" s="11">
+        <f t="shared" si="0"/>
+        <v>3.5611164581328092</v>
+      </c>
+      <c r="H23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="7">
+        <v>37</v>
+      </c>
+      <c r="B24">
         <v>109.1</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24">
         <v>110.1</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24">
         <v>109.6</v>
       </c>
       <c r="E24">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F24">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F24" s="11">
+        <f t="shared" si="0"/>
+        <v>1.8587360594795539</v>
+      </c>
+      <c r="H24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="7">
+        <v>38</v>
+      </c>
+      <c r="B25">
         <v>112.4</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25">
         <v>114.9</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25">
         <v>113.6</v>
       </c>
       <c r="E25">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F25">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F25" s="11">
+        <f t="shared" si="0"/>
+        <v>3.6496350364963508</v>
+      </c>
+      <c r="H25" s="11"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="7">
+        <v>39</v>
+      </c>
+      <c r="B26">
         <v>116.8</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26">
         <v>119.7</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26">
         <v>118.3</v>
       </c>
       <c r="E26">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F26">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F26" s="11">
+        <f t="shared" si="0"/>
+        <v>4.1373239436619746</v>
+      </c>
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="7">
+        <v>40</v>
+      </c>
+      <c r="B27">
         <v>122.7</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27">
         <v>125.3</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27">
         <v>124</v>
       </c>
       <c r="E27">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F27">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F27" s="11">
+        <f t="shared" si="0"/>
+        <v>4.8182586644125127</v>
+      </c>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="7">
+        <v>41</v>
+      </c>
+      <c r="B28">
         <v>128.69999999999999</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28">
         <v>132.6</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28">
         <v>130.69999999999999</v>
       </c>
       <c r="E28">
         <v>6.1</v>
       </c>
-      <c r="F28">
-        <v>5.4</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28" s="11">
+        <f t="shared" si="0"/>
+        <v>5.4032258064516041</v>
+      </c>
+      <c r="G28" s="5">
         <f>$D$50/D28</f>
         <v>1.7566488140780414</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="7">
+        <v>42</v>
+      </c>
+      <c r="B29">
         <v>135.19999999999999</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29">
         <v>137.19999999999999</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29">
         <v>136.19999999999999</v>
       </c>
       <c r="E29">
         <v>3.1</v>
       </c>
-      <c r="F29">
-        <v>4.2</v>
-      </c>
-      <c r="G29" s="6">
-        <f t="shared" ref="G29:G56" si="0">$D$50/D29</f>
+      <c r="F29" s="11">
+        <f t="shared" si="0"/>
+        <v>4.2081101759755173</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" ref="G29:G56" si="1">$D$50/D29</f>
         <v>1.6857121879588841</v>
       </c>
+      <c r="H29" s="11"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="7">
+        <v>43</v>
+      </c>
+      <c r="B30">
         <v>139.19999999999999</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30">
         <v>141.4</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30">
         <v>140.30000000000001</v>
       </c>
       <c r="E30">
         <v>2.9</v>
       </c>
-      <c r="F30">
-        <v>3</v>
-      </c>
-      <c r="G30" s="6">
-        <f t="shared" si="0"/>
+      <c r="F30" s="11">
+        <f t="shared" si="0"/>
+        <v>3.0102790014684455</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" si="1"/>
         <v>1.6364504632929435</v>
       </c>
+      <c r="H30" s="11"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="4"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="7">
+        <v>44</v>
+      </c>
+      <c r="B31">
         <v>143.69999999999999</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31">
         <v>145.30000000000001</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31">
         <v>144.5</v>
       </c>
       <c r="E31">
         <v>2.7</v>
       </c>
-      <c r="F31">
-        <v>3</v>
-      </c>
-      <c r="G31" s="6">
-        <f t="shared" si="0"/>
+      <c r="F31" s="11">
+        <f t="shared" si="0"/>
+        <v>2.9935851746257933</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="1"/>
         <v>1.5888858131487889</v>
       </c>
+      <c r="H31" s="11"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="O31" s="4"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="7">
+        <v>45</v>
+      </c>
+      <c r="B32">
         <v>147.19999999999999</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32">
         <v>149.30000000000001</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32">
         <v>148.19999999999999</v>
       </c>
       <c r="E32">
         <v>2.7</v>
       </c>
-      <c r="F32">
-        <v>2.6</v>
-      </c>
-      <c r="G32" s="6">
-        <f t="shared" si="0"/>
+      <c r="F32" s="11">
+        <f t="shared" si="0"/>
+        <v>2.5605536332179852</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" si="1"/>
         <v>1.5492172739541161</v>
       </c>
+      <c r="H32" s="11"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="4"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="7">
+        <v>46</v>
+      </c>
+      <c r="B33">
         <v>151.5</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33">
         <v>153.19999999999999</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33">
         <v>152.4</v>
       </c>
       <c r="E33">
         <v>2.5</v>
       </c>
-      <c r="F33">
-        <v>2.8</v>
-      </c>
-      <c r="G33" s="6">
-        <f t="shared" si="0"/>
+      <c r="F33" s="11">
+        <f t="shared" si="0"/>
+        <v>2.8340080971660035</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" si="1"/>
         <v>1.5065223097112861</v>
       </c>
+      <c r="H33" s="11"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="O33" s="4"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="7">
+        <v>47</v>
+      </c>
+      <c r="B34">
         <v>155.80000000000001</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34">
         <v>157.9</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34">
         <v>156.9</v>
       </c>
       <c r="E34">
         <v>3.3</v>
       </c>
-      <c r="F34">
-        <v>3</v>
-      </c>
-      <c r="G34" s="6">
-        <f t="shared" si="0"/>
+      <c r="F34" s="11">
+        <f t="shared" si="0"/>
+        <v>2.9527559055118111</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" si="1"/>
         <v>1.4633142128744423</v>
       </c>
+      <c r="H34" s="11"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
-      <c r="O34" s="4"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="7">
+        <v>48</v>
+      </c>
+      <c r="B35">
         <v>159.9</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35">
         <v>161.19999999999999</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35">
         <v>160.5</v>
       </c>
       <c r="E35">
         <v>1.7</v>
       </c>
-      <c r="F35">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G35" s="6">
-        <f t="shared" si="0"/>
+      <c r="F35" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2944550669216026</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" si="1"/>
         <v>1.4304922118380061</v>
       </c>
+      <c r="H35" s="11"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="4"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="7">
+        <v>49</v>
+      </c>
+      <c r="B36">
         <v>162.30000000000001</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36">
         <v>163.69999999999999</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36">
         <v>163</v>
       </c>
       <c r="E36">
         <v>1.6</v>
       </c>
-      <c r="F36">
-        <v>1.6</v>
-      </c>
-      <c r="G36" s="6">
-        <f t="shared" si="0"/>
+      <c r="F36" s="11">
+        <f t="shared" si="0"/>
+        <v>1.557632398753894</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" si="1"/>
         <v>1.4085521472392637</v>
       </c>
+      <c r="H36" s="11"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="4"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O36" s="3"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="7">
+        <v>50</v>
+      </c>
+      <c r="B37">
         <v>165.4</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37">
         <v>167.8</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37">
         <v>166.6</v>
       </c>
       <c r="E37">
         <v>2.7</v>
       </c>
-      <c r="F37">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G37" s="6">
-        <f t="shared" si="0"/>
+      <c r="F37" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2085889570552113</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" si="1"/>
         <v>1.3781152460984394</v>
       </c>
+      <c r="H37" s="11"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="4"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O37" s="3"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="7">
+        <v>51</v>
+      </c>
+      <c r="B38">
         <v>170.8</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38">
         <v>173.6</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38">
         <v>172.2</v>
       </c>
       <c r="E38">
         <v>3.4</v>
       </c>
-      <c r="F38">
-        <v>3.4</v>
-      </c>
-      <c r="G38" s="6">
-        <f t="shared" si="0"/>
+      <c r="F38" s="11">
+        <f t="shared" si="0"/>
+        <v>3.3613445378151225</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" si="1"/>
         <v>1.3332984901277585</v>
       </c>
+      <c r="H38" s="11"/>
       <c r="M38" s="2"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="4"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N38" s="4"/>
+      <c r="O38" s="3"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" s="7">
+        <v>52</v>
+      </c>
+      <c r="B39">
         <v>176.6</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39">
         <v>177.5</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39">
         <v>177.1</v>
       </c>
       <c r="E39">
         <v>1.6</v>
       </c>
-      <c r="F39">
-        <v>2.8</v>
-      </c>
-      <c r="G39" s="6">
-        <f t="shared" si="0"/>
+      <c r="F39" s="11">
+        <f t="shared" si="0"/>
+        <v>2.8455284552845561</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="shared" si="1"/>
         <v>1.2964088085827217</v>
       </c>
+      <c r="H39" s="11"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="4"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="7">
+        <v>53</v>
+      </c>
+      <c r="B40">
         <v>178.9</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40">
         <v>180.9</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40">
         <v>179.9</v>
       </c>
       <c r="E40">
         <v>2.4</v>
       </c>
-      <c r="F40">
-        <v>1.6</v>
-      </c>
-      <c r="G40" s="6">
-        <f t="shared" si="0"/>
+      <c r="F40" s="11">
+        <f t="shared" si="0"/>
+        <v>1.5810276679841961</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" si="1"/>
         <v>1.276231239577543</v>
       </c>
+      <c r="H40" s="11"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="4"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="7">
+        <v>54</v>
+      </c>
+      <c r="B41">
         <v>183.3</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41">
         <v>184.6</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41">
         <v>184</v>
       </c>
       <c r="E41">
         <v>1.9</v>
       </c>
-      <c r="F41">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G41" s="6">
-        <f t="shared" si="0"/>
+      <c r="F41" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2790439132851552</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" si="1"/>
         <v>1.2477934782608695</v>
       </c>
+      <c r="H41" s="11"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-      <c r="O41" s="4"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="7">
+        <v>55</v>
+      </c>
+      <c r="B42">
         <v>187.6</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42">
         <v>190.2</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42">
         <v>188.9</v>
       </c>
       <c r="E42">
         <v>3.3</v>
       </c>
-      <c r="F42">
-        <v>2.7</v>
-      </c>
-      <c r="G42" s="6">
-        <f t="shared" si="0"/>
+      <c r="F42" s="11">
+        <f t="shared" si="0"/>
+        <v>2.6630434782608727</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="1"/>
         <v>1.2154261514028586</v>
       </c>
+      <c r="H42" s="11"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="4"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="7">
+        <v>56</v>
+      </c>
+      <c r="B43">
         <v>193.2</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43">
         <v>197.4</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43">
         <v>195.3</v>
       </c>
       <c r="E43">
         <v>3.4</v>
       </c>
-      <c r="F43">
-        <v>3.4</v>
-      </c>
-      <c r="G43" s="6">
-        <f t="shared" si="0"/>
+      <c r="F43" s="11">
+        <f t="shared" si="0"/>
+        <v>3.3880359978824806</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" si="1"/>
         <v>1.1755965181771633</v>
       </c>
+      <c r="H43" s="11"/>
       <c r="M43" s="2"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="4"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N43" s="4"/>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" s="7">
+        <v>57</v>
+      </c>
+      <c r="B44">
         <v>200.6</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44">
         <v>202.6</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44">
         <v>201.6</v>
       </c>
       <c r="E44">
         <v>2.5</v>
       </c>
-      <c r="F44">
-        <v>3.2</v>
-      </c>
-      <c r="G44" s="6">
-        <f t="shared" si="0"/>
+      <c r="F44" s="11">
+        <f t="shared" si="0"/>
+        <v>3.2258064516128941</v>
+      </c>
+      <c r="G44" s="5">
+        <f t="shared" si="1"/>
         <v>1.1388591269841271</v>
       </c>
+      <c r="H44" s="11"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
-      <c r="O44" s="4"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="8">
+        <v>58</v>
+      </c>
+      <c r="B45">
         <v>205.709</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45">
         <v>208.976</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45">
         <v>207.34200000000001</v>
       </c>
       <c r="E45">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F45">
-        <v>2.8</v>
-      </c>
-      <c r="G45" s="6">
-        <f t="shared" si="0"/>
+      <c r="F45" s="11">
+        <f t="shared" si="0"/>
+        <v>2.8482142857142949</v>
+      </c>
+      <c r="G45" s="5">
+        <f t="shared" si="1"/>
         <v>1.107320272786025</v>
       </c>
+      <c r="H45" s="11"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="4"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="8">
+        <v>59</v>
+      </c>
+      <c r="B46">
         <v>214.429</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46">
         <v>216.17699999999999</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46">
         <v>215.303</v>
       </c>
       <c r="E46">
         <v>0.1</v>
       </c>
-      <c r="F46">
-        <v>3.8</v>
-      </c>
-      <c r="G46" s="6">
-        <f t="shared" si="0"/>
+      <c r="F46" s="11">
+        <f t="shared" si="0"/>
+        <v>3.8395501152684854</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" si="1"/>
         <v>1.0663762232760343</v>
       </c>
+      <c r="H46" s="11"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="4"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="8">
+        <v>60</v>
+      </c>
+      <c r="B47">
         <v>213.13900000000001</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47">
         <v>215.935</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47">
         <v>214.53700000000001</v>
       </c>
       <c r="E47">
         <v>2.7</v>
       </c>
-      <c r="F47">
-        <v>-0.4</v>
-      </c>
-      <c r="G47" s="6">
-        <f t="shared" si="0"/>
+      <c r="F47" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.35577767146764844</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" si="1"/>
         <v>1.0701836979169095</v>
       </c>
+      <c r="H47" s="11"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
-      <c r="O47" s="4"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="8">
+        <v>61</v>
+      </c>
+      <c r="B48">
         <v>217.535</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48">
         <v>218.57599999999999</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48">
         <v>218.05600000000001</v>
       </c>
       <c r="E48">
         <v>1.5</v>
       </c>
-      <c r="F48">
-        <v>1.6</v>
-      </c>
-      <c r="G48" s="6">
-        <f t="shared" si="0"/>
+      <c r="F48" s="11">
+        <f t="shared" si="0"/>
+        <v>1.6402765024214963</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" si="1"/>
         <v>1.0529130131709286</v>
       </c>
+      <c r="H48" s="11"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="4"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49" s="8">
+        <v>62</v>
+      </c>
+      <c r="B49">
         <v>223.59800000000001</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49">
         <v>226.28</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49">
         <v>224.93899999999999</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
-      <c r="F49">
-        <v>3.2</v>
-      </c>
-      <c r="G49" s="6">
-        <f t="shared" si="0"/>
+      <c r="F49" s="11">
+        <f t="shared" si="0"/>
+        <v>3.1565285981582627</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" si="1"/>
         <v>1.0206944993976144</v>
       </c>
+      <c r="H49" s="11"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="4"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="1:15" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="14">
+        <v>228.85</v>
+      </c>
+      <c r="C50" s="14">
+        <v>230.33799999999999</v>
+      </c>
+      <c r="D50" s="14">
+        <v>229.59399999999999</v>
+      </c>
+      <c r="E50" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="F50" s="15">
+        <f t="shared" si="0"/>
+        <v>2.069449939761447</v>
+      </c>
+      <c r="G50" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="18"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="8">
-        <v>228.85</v>
-      </c>
-      <c r="C50" s="8">
-        <v>230.33799999999999</v>
-      </c>
-      <c r="D50" s="8">
-        <v>229.59399999999999</v>
-      </c>
-      <c r="E50">
-        <v>1.7</v>
-      </c>
-      <c r="F50">
-        <v>2.1</v>
-      </c>
-      <c r="G50" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="4"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="8">
+      <c r="B51">
         <v>232.36600000000001</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51">
         <v>233.548</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51">
         <v>232.95699999999999</v>
       </c>
       <c r="E51">
         <v>1.5</v>
       </c>
-      <c r="F51">
-        <v>1.5</v>
-      </c>
-      <c r="G51" s="6">
-        <f t="shared" si="0"/>
+      <c r="F51" s="11">
+        <f t="shared" si="0"/>
+        <v>1.4647595320435203</v>
+      </c>
+      <c r="G51" s="5">
+        <f t="shared" si="1"/>
         <v>0.98556385942470071</v>
       </c>
+      <c r="H51" s="11"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="4"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="8">
+        <v>65</v>
+      </c>
+      <c r="B52">
         <v>236.38399999999999</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52">
         <v>237.08799999999999</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52">
         <v>236.73599999999999</v>
       </c>
       <c r="E52">
         <v>0.8</v>
       </c>
-      <c r="F52">
-        <v>1.6</v>
-      </c>
-      <c r="G52" s="6">
-        <f t="shared" si="0"/>
+      <c r="F52" s="11">
+        <f t="shared" si="0"/>
+        <v>1.6221877857286953</v>
+      </c>
+      <c r="G52" s="5">
+        <f t="shared" si="1"/>
         <v>0.96983137334414704</v>
       </c>
+      <c r="H52" s="11"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="4"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="8">
+        <v>66</v>
+      </c>
+      <c r="B53">
         <v>236.26499999999999</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53">
         <v>237.76900000000001</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53">
         <v>237.017</v>
       </c>
       <c r="E53">
         <v>0.7</v>
       </c>
-      <c r="F53">
-        <v>0.1</v>
-      </c>
-      <c r="G53" s="6">
-        <f t="shared" si="0"/>
+      <c r="F53" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11869762097864538</v>
+      </c>
+      <c r="G53" s="5">
+        <f t="shared" si="1"/>
         <v>0.9686815713640794</v>
       </c>
+      <c r="H53" s="11"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="4"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" s="8">
+        <v>67</v>
+      </c>
+      <c r="B54">
         <v>238.77799999999999</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54">
         <v>241.23699999999999</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54">
         <v>240.00700000000001</v>
       </c>
       <c r="E54">
         <v>2.1</v>
       </c>
-      <c r="F54">
-        <v>1.3</v>
-      </c>
-      <c r="G54" s="6">
-        <f t="shared" si="0"/>
+      <c r="F54" s="11">
+        <f t="shared" si="0"/>
+        <v>1.2615128872612551</v>
+      </c>
+      <c r="G54" s="5">
+        <f t="shared" si="1"/>
         <v>0.95661376543184151</v>
       </c>
+      <c r="H54" s="11"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="4"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="8">
+        <v>68</v>
+      </c>
+      <c r="B55">
         <v>244.07599999999999</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55">
         <v>246.16300000000001</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55">
         <v>245.12</v>
       </c>
       <c r="E55">
         <v>2.1</v>
       </c>
-      <c r="F55">
-        <v>2.1</v>
-      </c>
-      <c r="G55" s="6">
-        <f t="shared" si="0"/>
+      <c r="F55" s="11">
+        <f t="shared" si="0"/>
+        <v>2.1303545313261694</v>
+      </c>
+      <c r="G55" s="5">
+        <f t="shared" si="1"/>
         <v>0.93665959530026111</v>
       </c>
+      <c r="H55" s="11"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="4"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" s="8">
+        <v>69</v>
+      </c>
+      <c r="B56">
         <v>250.089</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56">
         <v>252.125</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56">
         <v>251.107</v>
       </c>
       <c r="E56">
         <v>1.9</v>
       </c>
-      <c r="F56">
-        <v>2.4</v>
-      </c>
-      <c r="G56" s="6">
-        <f t="shared" si="0"/>
+      <c r="F56" s="11">
+        <f t="shared" si="0"/>
+        <v>2.4424771540469949</v>
+      </c>
+      <c r="G56" s="5">
+        <f t="shared" si="1"/>
         <v>0.9143273584567535</v>
       </c>
+      <c r="H56" s="11"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
-      <c r="O56" s="4"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="8">
+        <v>70</v>
+      </c>
+      <c r="B57">
         <v>254.41200000000001</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57">
         <v>256.90300000000002</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57">
         <v>255.65700000000001</v>
       </c>
       <c r="E57">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F57">
-        <v>1.8</v>
-      </c>
-      <c r="G57" s="6">
+      <c r="F57" s="11">
+        <f t="shared" si="0"/>
+        <v>1.811976567757972</v>
+      </c>
+      <c r="G57" s="5">
         <f>$D$50/D57</f>
         <v>0.89805481563188172</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="8">
+        <v>71</v>
+      </c>
+      <c r="B58">
         <v>257.55700000000002</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58">
         <v>260.065</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58">
         <v>258.81099999999998</v>
       </c>
       <c r="E58">
         <v>1.4</v>
       </c>
-      <c r="F58">
-        <v>1.2</v>
-      </c>
-      <c r="G58" s="6">
+      <c r="F58" s="11">
+        <f t="shared" si="0"/>
+        <v>1.2336841940568684</v>
+      </c>
+      <c r="G58" s="5">
         <f>$D$50/D58</f>
         <v>0.88711067149387013</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="10">
         <v>266.23599999999999</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="10">
         <v>275.70299999999997</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="10">
         <v>270.97000000000003</v>
       </c>
-      <c r="E59">
-        <v>7</v>
-      </c>
-      <c r="F59">
-        <v>4.7</v>
-      </c>
-      <c r="G59" s="6">
-        <f>$D$50/D59</f>
+      <c r="F59" s="12">
+        <f t="shared" si="0"/>
+        <v>4.69802288156224</v>
+      </c>
+      <c r="G59" s="13">
+        <f t="shared" ref="G59:G62" si="2">$D$50/D59</f>
         <v>0.84730412960844359</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="10">
         <v>288.34699999999998</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="10">
         <v>296.96300000000002</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="10">
         <v>292.65499999999997</v>
       </c>
-      <c r="E60">
-        <v>6.5</v>
-      </c>
-      <c r="F60">
-        <v>8</v>
-      </c>
-      <c r="G60" s="6">
-        <f>$D$50/D60</f>
+      <c r="F60" s="12">
+        <f t="shared" si="0"/>
+        <v>8.0027309296231852</v>
+      </c>
+      <c r="G60" s="13">
+        <f t="shared" si="2"/>
         <v>0.78452102304761584</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="10">
         <v>302.40800000000002</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="10">
         <v>306.99599999999998</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="10">
         <v>304.702</v>
       </c>
-      <c r="G61" s="6">
-        <f>$D$50/D61</f>
+      <c r="F61" s="12">
+        <f t="shared" si="0"/>
+        <v>4.116451111376886</v>
+      </c>
+      <c r="G61" s="13">
+        <f t="shared" si="2"/>
         <v>0.75350342301658668</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G62" s="6"/>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="10">
+        <v>312.14499999999998</v>
+      </c>
+      <c r="C62" s="10">
+        <v>315.233</v>
+      </c>
+      <c r="D62" s="10">
+        <v>313.68900000000002</v>
+      </c>
+      <c r="F62" s="12">
+        <f t="shared" si="0"/>
+        <v>2.9494391241278439</v>
+      </c>
+      <c r="G62" s="13">
+        <f t="shared" si="2"/>
+        <v>0.73191600598044548</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5244E89-83D3-4B29-AEF0-46A544AD747B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77210D78-59AC-4EA4-B0A4-29524D273C4B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3FAA340-9F2E-42C4-864E-0A8973833BED}"/>
 </file>